--- a/output_phyto/phyto_Intermediate_palmer_2010.xlsx
+++ b/output_phyto/phyto_Intermediate_palmer_2010.xlsx
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_1</t>
+    <t xml:space="preserve">X3</t>
   </si>
   <si>
     <t xml:space="preserve">10.1016/j.epsl.2010.03.023</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/phytoplankton_palmer_2010.xlsx</t>
+    <t xml:space="preserve">phytoplankton_palmer_2010_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1475,97 +1475,97 @@
     <t xml:space="preserve">Mk37_2</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Palmer_2010_32</t>
+    <t xml:space="preserve">X10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140</t>
   </si>
 </sst>
 </file>
@@ -1573,7 +1573,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1639,12 +1639,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1758,7 +1752,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1857,7 +1851,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2583,7 +2576,7 @@
       <c r="B5" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" t="s">
         <v>272</v>
       </c>
       <c r="D5" t="s">
@@ -2601,8 +2594,8 @@
       <c r="H5" t="n">
         <v>0.0078</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.004</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2619,8 +2612,8 @@
       <c r="N5" t="n">
         <v>-22.55</v>
       </c>
-      <c r="O5" t="e">
-        <v>#N/A</v>
+      <c r="O5" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P5" t="e">
         <v>#N/A</v>
@@ -2658,20 +2651,20 @@
       <c r="AA5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB5" t="e">
-        <v>#N/A</v>
+      <c r="AB5" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF5" t="e">
-        <v>#N/A</v>
+      <c r="AD5" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG5" t="e">
         <v>#N/A</v>
@@ -2693,7 +2686,7 @@
       <c r="B6" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" t="s">
         <v>272</v>
       </c>
       <c r="D6" t="s">
@@ -2711,8 +2704,8 @@
       <c r="H6" t="n">
         <v>0.0086</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.004</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2729,8 +2722,8 @@
       <c r="N6" t="n">
         <v>-22.87</v>
       </c>
-      <c r="O6" t="e">
-        <v>#N/A</v>
+      <c r="O6" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P6" t="e">
         <v>#N/A</v>
@@ -2768,20 +2761,20 @@
       <c r="AA6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB6" t="e">
-        <v>#N/A</v>
+      <c r="AB6" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF6" t="e">
-        <v>#N/A</v>
+      <c r="AD6" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG6" t="e">
         <v>#N/A</v>
@@ -2803,7 +2796,7 @@
       <c r="B7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" t="s">
         <v>272</v>
       </c>
       <c r="D7" t="s">
@@ -2821,8 +2814,8 @@
       <c r="H7" t="n">
         <v>0.0087</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.004</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2839,8 +2832,8 @@
       <c r="N7" t="n">
         <v>-24.05</v>
       </c>
-      <c r="O7" t="e">
-        <v>#N/A</v>
+      <c r="O7" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P7" t="e">
         <v>#N/A</v>
@@ -2878,20 +2871,20 @@
       <c r="AA7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB7" t="e">
-        <v>#N/A</v>
+      <c r="AB7" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF7" t="e">
-        <v>#N/A</v>
+      <c r="AD7" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG7" t="e">
         <v>#N/A</v>
@@ -2913,7 +2906,7 @@
       <c r="B8" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" t="s">
         <v>272</v>
       </c>
       <c r="D8" t="s">
@@ -2931,8 +2924,8 @@
       <c r="H8" t="n">
         <v>0.0091</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.004</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -2949,8 +2942,8 @@
       <c r="N8" t="n">
         <v>-22.25</v>
       </c>
-      <c r="O8" t="e">
-        <v>#N/A</v>
+      <c r="O8" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P8" t="e">
         <v>#N/A</v>
@@ -2988,20 +2981,20 @@
       <c r="AA8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB8" t="e">
-        <v>#N/A</v>
+      <c r="AB8" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF8" t="e">
-        <v>#N/A</v>
+      <c r="AD8" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG8" t="e">
         <v>#N/A</v>
@@ -3023,7 +3016,7 @@
       <c r="B9" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" t="s">
         <v>272</v>
       </c>
       <c r="D9" t="s">
@@ -3041,8 +3034,8 @@
       <c r="H9" t="n">
         <v>0.0095</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.004</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -3059,8 +3052,8 @@
       <c r="N9" t="n">
         <v>-22.28</v>
       </c>
-      <c r="O9" t="e">
-        <v>#N/A</v>
+      <c r="O9" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P9" t="e">
         <v>#N/A</v>
@@ -3098,20 +3091,20 @@
       <c r="AA9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB9" t="e">
-        <v>#N/A</v>
+      <c r="AB9" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF9" t="e">
-        <v>#N/A</v>
+      <c r="AD9" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG9" t="e">
         <v>#N/A</v>
@@ -3133,7 +3126,7 @@
       <c r="B10" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" t="s">
         <v>272</v>
       </c>
       <c r="D10" t="s">
@@ -3151,8 +3144,8 @@
       <c r="H10" t="n">
         <v>0.0105</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.004</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3169,8 +3162,8 @@
       <c r="N10" t="n">
         <v>-23.44</v>
       </c>
-      <c r="O10" t="e">
-        <v>#N/A</v>
+      <c r="O10" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P10" t="e">
         <v>#N/A</v>
@@ -3208,20 +3201,20 @@
       <c r="AA10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB10" t="e">
-        <v>#N/A</v>
+      <c r="AB10" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF10" t="e">
-        <v>#N/A</v>
+      <c r="AD10" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG10" t="e">
         <v>#N/A</v>
@@ -3243,7 +3236,7 @@
       <c r="B11" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
       <c r="D11" t="s">
@@ -3261,8 +3254,8 @@
       <c r="H11" t="n">
         <v>0.0111</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.004</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3279,8 +3272,8 @@
       <c r="N11" t="n">
         <v>-23.03</v>
       </c>
-      <c r="O11" t="e">
-        <v>#N/A</v>
+      <c r="O11" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P11" t="e">
         <v>#N/A</v>
@@ -3318,20 +3311,20 @@
       <c r="AA11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB11" t="e">
-        <v>#N/A</v>
+      <c r="AB11" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF11" t="e">
-        <v>#N/A</v>
+      <c r="AD11" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG11" t="e">
         <v>#N/A</v>
@@ -3353,7 +3346,7 @@
       <c r="B12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" t="s">
         <v>272</v>
       </c>
       <c r="D12" t="s">
@@ -3371,8 +3364,8 @@
       <c r="H12" t="n">
         <v>0.012</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.004</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3389,8 +3382,8 @@
       <c r="N12" t="n">
         <v>-24.17</v>
       </c>
-      <c r="O12" t="e">
-        <v>#N/A</v>
+      <c r="O12" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P12" t="e">
         <v>#N/A</v>
@@ -3428,20 +3421,20 @@
       <c r="AA12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB12" t="e">
-        <v>#N/A</v>
+      <c r="AB12" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF12" t="e">
-        <v>#N/A</v>
+      <c r="AD12" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG12" t="e">
         <v>#N/A</v>
@@ -3463,7 +3456,7 @@
       <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" t="s">
         <v>272</v>
       </c>
       <c r="D13" t="s">
@@ -3481,8 +3474,8 @@
       <c r="H13" t="n">
         <v>0.0125</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.004</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3499,8 +3492,8 @@
       <c r="N13" t="n">
         <v>-21.88</v>
       </c>
-      <c r="O13" t="e">
-        <v>#N/A</v>
+      <c r="O13" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P13" t="e">
         <v>#N/A</v>
@@ -3538,20 +3531,20 @@
       <c r="AA13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB13" t="e">
-        <v>#N/A</v>
+      <c r="AB13" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF13" t="e">
-        <v>#N/A</v>
+      <c r="AD13" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG13" t="e">
         <v>#N/A</v>
@@ -3573,7 +3566,7 @@
       <c r="B14" t="s">
         <v>271</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" t="s">
         <v>272</v>
       </c>
       <c r="D14" t="s">
@@ -3591,8 +3584,8 @@
       <c r="H14" t="n">
         <v>0.0135</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.004</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3609,8 +3602,8 @@
       <c r="N14" t="n">
         <v>-22.96</v>
       </c>
-      <c r="O14" t="e">
-        <v>#N/A</v>
+      <c r="O14" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P14" t="e">
         <v>#N/A</v>
@@ -3648,20 +3641,20 @@
       <c r="AA14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB14" t="e">
-        <v>#N/A</v>
+      <c r="AB14" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF14" t="e">
-        <v>#N/A</v>
+      <c r="AD14" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG14" t="e">
         <v>#N/A</v>
@@ -3683,7 +3676,7 @@
       <c r="B15" t="s">
         <v>271</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" t="s">
         <v>272</v>
       </c>
       <c r="D15" t="s">
@@ -3701,8 +3694,8 @@
       <c r="H15" t="n">
         <v>0.014</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.004</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3719,8 +3712,8 @@
       <c r="N15" t="n">
         <v>-23.31</v>
       </c>
-      <c r="O15" t="e">
-        <v>#N/A</v>
+      <c r="O15" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P15" t="e">
         <v>#N/A</v>
@@ -3758,20 +3751,20 @@
       <c r="AA15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB15" t="e">
-        <v>#N/A</v>
+      <c r="AB15" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF15" t="e">
-        <v>#N/A</v>
+      <c r="AD15" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG15" t="e">
         <v>#N/A</v>
@@ -3793,7 +3786,7 @@
       <c r="B16" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" t="s">
         <v>272</v>
       </c>
       <c r="D16" t="s">
@@ -3811,8 +3804,8 @@
       <c r="H16" t="n">
         <v>0.0145</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.004</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3829,8 +3822,8 @@
       <c r="N16" t="n">
         <v>-22.86</v>
       </c>
-      <c r="O16" t="e">
-        <v>#N/A</v>
+      <c r="O16" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P16" t="e">
         <v>#N/A</v>
@@ -3868,20 +3861,20 @@
       <c r="AA16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB16" t="e">
-        <v>#N/A</v>
+      <c r="AB16" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF16" t="e">
-        <v>#N/A</v>
+      <c r="AD16" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG16" t="e">
         <v>#N/A</v>
@@ -3903,7 +3896,7 @@
       <c r="B17" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" t="s">
         <v>272</v>
       </c>
       <c r="D17" t="s">
@@ -3921,8 +3914,8 @@
       <c r="H17" t="n">
         <v>0.0156</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.004</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -3939,8 +3932,8 @@
       <c r="N17" t="n">
         <v>-23.67</v>
       </c>
-      <c r="O17" t="e">
-        <v>#N/A</v>
+      <c r="O17" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P17" t="e">
         <v>#N/A</v>
@@ -3978,20 +3971,20 @@
       <c r="AA17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB17" t="e">
-        <v>#N/A</v>
+      <c r="AB17" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF17" t="e">
-        <v>#N/A</v>
+      <c r="AD17" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG17" t="e">
         <v>#N/A</v>
@@ -4013,7 +4006,7 @@
       <c r="B18" t="s">
         <v>271</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" t="s">
         <v>272</v>
       </c>
       <c r="D18" t="s">
@@ -4031,8 +4024,8 @@
       <c r="H18" t="n">
         <v>0.016</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.004</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -4049,8 +4042,8 @@
       <c r="N18" t="n">
         <v>-23.49</v>
       </c>
-      <c r="O18" t="e">
-        <v>#N/A</v>
+      <c r="O18" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P18" t="e">
         <v>#N/A</v>
@@ -4088,20 +4081,20 @@
       <c r="AA18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB18" t="e">
-        <v>#N/A</v>
+      <c r="AB18" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF18" t="e">
-        <v>#N/A</v>
+      <c r="AD18" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG18" t="e">
         <v>#N/A</v>
@@ -4123,7 +4116,7 @@
       <c r="B19" t="s">
         <v>271</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" t="s">
         <v>272</v>
       </c>
       <c r="D19" t="s">
@@ -4141,8 +4134,8 @@
       <c r="H19" t="n">
         <v>0.0164</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.004</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -4159,8 +4152,8 @@
       <c r="N19" t="n">
         <v>-23.72</v>
       </c>
-      <c r="O19" t="e">
-        <v>#N/A</v>
+      <c r="O19" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P19" t="e">
         <v>#N/A</v>
@@ -4198,20 +4191,20 @@
       <c r="AA19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB19" t="e">
-        <v>#N/A</v>
+      <c r="AB19" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF19" t="e">
-        <v>#N/A</v>
+      <c r="AD19" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG19" t="e">
         <v>#N/A</v>
@@ -4233,7 +4226,7 @@
       <c r="B20" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" t="s">
         <v>272</v>
       </c>
       <c r="D20" t="s">
@@ -4251,8 +4244,8 @@
       <c r="H20" t="n">
         <v>0.017</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.004</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -4269,8 +4262,8 @@
       <c r="N20" t="n">
         <v>-24.04</v>
       </c>
-      <c r="O20" t="e">
-        <v>#N/A</v>
+      <c r="O20" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P20" t="e">
         <v>#N/A</v>
@@ -4308,20 +4301,20 @@
       <c r="AA20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB20" t="e">
-        <v>#N/A</v>
+      <c r="AB20" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF20" t="e">
-        <v>#N/A</v>
+      <c r="AD20" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG20" t="e">
         <v>#N/A</v>
@@ -4343,7 +4336,7 @@
       <c r="B21" t="s">
         <v>271</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" t="s">
         <v>272</v>
       </c>
       <c r="D21" t="s">
@@ -4361,8 +4354,8 @@
       <c r="H21" t="n">
         <v>0.0175</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.004</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -4379,8 +4372,8 @@
       <c r="N21" t="n">
         <v>-23.74</v>
       </c>
-      <c r="O21" t="e">
-        <v>#N/A</v>
+      <c r="O21" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P21" t="e">
         <v>#N/A</v>
@@ -4418,20 +4411,20 @@
       <c r="AA21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB21" t="e">
-        <v>#N/A</v>
+      <c r="AB21" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF21" t="e">
-        <v>#N/A</v>
+      <c r="AD21" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG21" t="e">
         <v>#N/A</v>
@@ -4453,7 +4446,7 @@
       <c r="B22" t="s">
         <v>271</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" t="s">
         <v>272</v>
       </c>
       <c r="D22" t="s">
@@ -4471,8 +4464,8 @@
       <c r="H22" t="n">
         <v>0.0187</v>
       </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+      <c r="I22" t="n">
+        <v>0.004</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -4489,8 +4482,8 @@
       <c r="N22" t="n">
         <v>-23.63</v>
       </c>
-      <c r="O22" t="e">
-        <v>#N/A</v>
+      <c r="O22" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P22" t="e">
         <v>#N/A</v>
@@ -4528,20 +4521,20 @@
       <c r="AA22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB22" t="e">
-        <v>#N/A</v>
+      <c r="AB22" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF22" t="e">
-        <v>#N/A</v>
+      <c r="AD22" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG22" t="e">
         <v>#N/A</v>
@@ -4563,7 +4556,7 @@
       <c r="B23" t="s">
         <v>271</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" t="s">
         <v>272</v>
       </c>
       <c r="D23" t="s">
@@ -4581,8 +4574,8 @@
       <c r="H23" t="n">
         <v>0.0215</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.004</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -4599,8 +4592,8 @@
       <c r="N23" t="n">
         <v>-22.01</v>
       </c>
-      <c r="O23" t="e">
-        <v>#N/A</v>
+      <c r="O23" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P23" t="e">
         <v>#N/A</v>
@@ -4638,20 +4631,20 @@
       <c r="AA23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB23" t="e">
-        <v>#N/A</v>
+      <c r="AB23" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF23" t="e">
-        <v>#N/A</v>
+      <c r="AD23" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG23" t="e">
         <v>#N/A</v>
@@ -4673,7 +4666,7 @@
       <c r="B24" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" t="s">
         <v>272</v>
       </c>
       <c r="D24" t="s">
@@ -4691,8 +4684,8 @@
       <c r="H24" t="n">
         <v>0.0221</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.004</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -4709,8 +4702,8 @@
       <c r="N24" t="n">
         <v>-22.34</v>
       </c>
-      <c r="O24" t="e">
-        <v>#N/A</v>
+      <c r="O24" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P24" t="e">
         <v>#N/A</v>
@@ -4748,20 +4741,20 @@
       <c r="AA24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB24" t="e">
-        <v>#N/A</v>
+      <c r="AB24" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF24" t="e">
-        <v>#N/A</v>
+      <c r="AD24" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG24" t="e">
         <v>#N/A</v>
@@ -4783,7 +4776,7 @@
       <c r="B25" t="s">
         <v>271</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" t="s">
         <v>272</v>
       </c>
       <c r="D25" t="s">
@@ -4801,8 +4794,8 @@
       <c r="H25" t="n">
         <v>0.0225</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.004</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -4819,8 +4812,8 @@
       <c r="N25" t="n">
         <v>-22.37</v>
       </c>
-      <c r="O25" t="e">
-        <v>#N/A</v>
+      <c r="O25" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P25" t="e">
         <v>#N/A</v>
@@ -4858,20 +4851,20 @@
       <c r="AA25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB25" t="e">
-        <v>#N/A</v>
+      <c r="AB25" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" t="e">
-        <v>#N/A</v>
+      <c r="AD25" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG25" t="e">
         <v>#N/A</v>
@@ -4893,7 +4886,7 @@
       <c r="B26" t="s">
         <v>271</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" t="s">
         <v>272</v>
       </c>
       <c r="D26" t="s">
@@ -4911,8 +4904,8 @@
       <c r="H26" t="n">
         <v>0.0236</v>
       </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+      <c r="I26" t="n">
+        <v>0.004</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -4929,8 +4922,8 @@
       <c r="N26" t="n">
         <v>-21.75</v>
       </c>
-      <c r="O26" t="e">
-        <v>#N/A</v>
+      <c r="O26" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P26" t="e">
         <v>#N/A</v>
@@ -4968,20 +4961,20 @@
       <c r="AA26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB26" t="e">
-        <v>#N/A</v>
+      <c r="AB26" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF26" t="e">
-        <v>#N/A</v>
+      <c r="AD26" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG26" t="e">
         <v>#N/A</v>
@@ -5003,7 +4996,7 @@
       <c r="B27" t="s">
         <v>271</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" t="s">
         <v>272</v>
       </c>
       <c r="D27" t="s">
@@ -5021,8 +5014,8 @@
       <c r="H27" t="n">
         <v>0.024</v>
       </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+      <c r="I27" t="n">
+        <v>0.004</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -5039,8 +5032,8 @@
       <c r="N27" t="n">
         <v>-21.79</v>
       </c>
-      <c r="O27" t="e">
-        <v>#N/A</v>
+      <c r="O27" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P27" t="e">
         <v>#N/A</v>
@@ -5078,20 +5071,20 @@
       <c r="AA27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB27" t="e">
-        <v>#N/A</v>
+      <c r="AB27" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF27" t="e">
-        <v>#N/A</v>
+      <c r="AD27" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG27" t="e">
         <v>#N/A</v>
@@ -5113,7 +5106,7 @@
       <c r="B28" t="s">
         <v>271</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" t="s">
         <v>272</v>
       </c>
       <c r="D28" t="s">
@@ -5131,8 +5124,8 @@
       <c r="H28" t="n">
         <v>0.0251</v>
       </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+      <c r="I28" t="n">
+        <v>0.004</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -5149,8 +5142,8 @@
       <c r="N28" t="n">
         <v>-21.32</v>
       </c>
-      <c r="O28" t="e">
-        <v>#N/A</v>
+      <c r="O28" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P28" t="e">
         <v>#N/A</v>
@@ -5188,20 +5181,20 @@
       <c r="AA28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB28" t="e">
-        <v>#N/A</v>
+      <c r="AB28" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF28" t="e">
-        <v>#N/A</v>
+      <c r="AD28" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG28" t="e">
         <v>#N/A</v>
@@ -5223,7 +5216,7 @@
       <c r="B29" t="s">
         <v>271</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" t="s">
         <v>272</v>
       </c>
       <c r="D29" t="s">
@@ -5241,8 +5234,8 @@
       <c r="H29" t="n">
         <v>0.0252</v>
       </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+      <c r="I29" t="n">
+        <v>0.004</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -5259,8 +5252,8 @@
       <c r="N29" t="n">
         <v>-23.13</v>
       </c>
-      <c r="O29" t="e">
-        <v>#N/A</v>
+      <c r="O29" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P29" t="e">
         <v>#N/A</v>
@@ -5298,20 +5291,20 @@
       <c r="AA29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB29" t="e">
-        <v>#N/A</v>
+      <c r="AB29" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF29" t="e">
-        <v>#N/A</v>
+      <c r="AD29" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG29" t="e">
         <v>#N/A</v>
@@ -5333,7 +5326,7 @@
       <c r="B30" t="s">
         <v>271</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" t="s">
         <v>272</v>
       </c>
       <c r="D30" t="s">
@@ -5351,8 +5344,8 @@
       <c r="H30" t="n">
         <v>0.026</v>
       </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+      <c r="I30" t="n">
+        <v>0.004</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -5369,8 +5362,8 @@
       <c r="N30" t="n">
         <v>-21.5</v>
       </c>
-      <c r="O30" t="e">
-        <v>#N/A</v>
+      <c r="O30" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P30" t="e">
         <v>#N/A</v>
@@ -5408,20 +5401,20 @@
       <c r="AA30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB30" t="e">
-        <v>#N/A</v>
+      <c r="AB30" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF30" t="e">
-        <v>#N/A</v>
+      <c r="AD30" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG30" t="e">
         <v>#N/A</v>
@@ -5443,7 +5436,7 @@
       <c r="B31" t="s">
         <v>271</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" t="s">
         <v>272</v>
       </c>
       <c r="D31" t="s">
@@ -5461,8 +5454,8 @@
       <c r="H31" t="n">
         <v>0.0262</v>
       </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+      <c r="I31" t="n">
+        <v>0.004</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -5479,8 +5472,8 @@
       <c r="N31" t="n">
         <v>-22.37</v>
       </c>
-      <c r="O31" t="e">
-        <v>#N/A</v>
+      <c r="O31" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P31" t="e">
         <v>#N/A</v>
@@ -5518,20 +5511,20 @@
       <c r="AA31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB31" t="e">
-        <v>#N/A</v>
+      <c r="AB31" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF31" t="e">
-        <v>#N/A</v>
+      <c r="AD31" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG31" t="e">
         <v>#N/A</v>
@@ -5553,7 +5546,7 @@
       <c r="B32" t="s">
         <v>271</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" t="s">
         <v>272</v>
       </c>
       <c r="D32" t="s">
@@ -5571,8 +5564,8 @@
       <c r="H32" t="n">
         <v>0.0266</v>
       </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+      <c r="I32" t="n">
+        <v>0.004</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -5589,8 +5582,8 @@
       <c r="N32" t="n">
         <v>-22.18</v>
       </c>
-      <c r="O32" t="e">
-        <v>#N/A</v>
+      <c r="O32" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P32" t="e">
         <v>#N/A</v>
@@ -5628,20 +5621,20 @@
       <c r="AA32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB32" t="e">
-        <v>#N/A</v>
+      <c r="AB32" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF32" t="e">
-        <v>#N/A</v>
+      <c r="AD32" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG32" t="e">
         <v>#N/A</v>
@@ -5663,7 +5656,7 @@
       <c r="B33" t="s">
         <v>271</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" t="s">
         <v>272</v>
       </c>
       <c r="D33" t="s">
@@ -5681,8 +5674,8 @@
       <c r="H33" t="n">
         <v>0.0269</v>
       </c>
-      <c r="I33" t="e">
-        <v>#N/A</v>
+      <c r="I33" t="n">
+        <v>0.004</v>
       </c>
       <c r="J33" t="e">
         <v>#N/A</v>
@@ -5699,8 +5692,8 @@
       <c r="N33" t="n">
         <v>-22.81</v>
       </c>
-      <c r="O33" t="e">
-        <v>#N/A</v>
+      <c r="O33" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P33" t="e">
         <v>#N/A</v>
@@ -5738,20 +5731,20 @@
       <c r="AA33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB33" t="e">
-        <v>#N/A</v>
+      <c r="AB33" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF33" t="e">
-        <v>#N/A</v>
+      <c r="AD33" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG33" t="e">
         <v>#N/A</v>
@@ -5773,7 +5766,7 @@
       <c r="B34" t="s">
         <v>271</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" t="s">
         <v>272</v>
       </c>
       <c r="D34" t="s">
@@ -5791,8 +5784,8 @@
       <c r="H34" t="n">
         <v>0.0275</v>
       </c>
-      <c r="I34" t="e">
-        <v>#N/A</v>
+      <c r="I34" t="n">
+        <v>0.004</v>
       </c>
       <c r="J34" t="e">
         <v>#N/A</v>
@@ -5809,8 +5802,8 @@
       <c r="N34" t="n">
         <v>-22.91</v>
       </c>
-      <c r="O34" t="e">
-        <v>#N/A</v>
+      <c r="O34" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P34" t="e">
         <v>#N/A</v>
@@ -5848,20 +5841,20 @@
       <c r="AA34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB34" t="e">
-        <v>#N/A</v>
+      <c r="AB34" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF34" t="e">
-        <v>#N/A</v>
+      <c r="AD34" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG34" t="e">
         <v>#N/A</v>
@@ -5883,7 +5876,7 @@
       <c r="B35" t="s">
         <v>271</v>
       </c>
-      <c r="C35" s="34" t="s">
+      <c r="C35" t="s">
         <v>272</v>
       </c>
       <c r="D35" t="s">
@@ -5901,8 +5894,8 @@
       <c r="H35" t="n">
         <v>0.028</v>
       </c>
-      <c r="I35" t="e">
-        <v>#N/A</v>
+      <c r="I35" t="n">
+        <v>0.004</v>
       </c>
       <c r="J35" t="e">
         <v>#N/A</v>
@@ -5919,8 +5912,8 @@
       <c r="N35" t="n">
         <v>-21.72</v>
       </c>
-      <c r="O35" t="e">
-        <v>#N/A</v>
+      <c r="O35" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P35" t="e">
         <v>#N/A</v>
@@ -5958,20 +5951,20 @@
       <c r="AA35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB35" t="e">
-        <v>#N/A</v>
+      <c r="AB35" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF35" t="e">
-        <v>#N/A</v>
+      <c r="AD35" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG35" t="e">
         <v>#N/A</v>
@@ -5993,7 +5986,7 @@
       <c r="B36" t="s">
         <v>271</v>
       </c>
-      <c r="C36" s="34" t="s">
+      <c r="C36" t="s">
         <v>272</v>
       </c>
       <c r="D36" t="s">
@@ -6011,8 +6004,8 @@
       <c r="H36" t="n">
         <v>0.029</v>
       </c>
-      <c r="I36" t="e">
-        <v>#N/A</v>
+      <c r="I36" t="n">
+        <v>0.004</v>
       </c>
       <c r="J36" t="e">
         <v>#N/A</v>
@@ -6029,8 +6022,8 @@
       <c r="N36" t="n">
         <v>-22.03</v>
       </c>
-      <c r="O36" t="e">
-        <v>#N/A</v>
+      <c r="O36" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P36" t="e">
         <v>#N/A</v>
@@ -6068,20 +6061,20 @@
       <c r="AA36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB36" t="e">
-        <v>#N/A</v>
+      <c r="AB36" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF36" t="e">
-        <v>#N/A</v>
+      <c r="AD36" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG36" t="e">
         <v>#N/A</v>
@@ -6382,40 +6375,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
